--- a/data/trans_dic/IP1008-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1008-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen trastornos huesos, articulaciones o musculares</t>
+          <t>Menores que padecen trastornos huesos, articulaciones o musculares (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,5</t>
+          <t>0,0; 5,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,04</t>
+          <t>0,0; 8,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,37</t>
+          <t>0,0; 5,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,68</t>
+          <t>0,0; 5,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,69</t>
+          <t>0,37; 3,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,96</t>
+          <t>0,0; 4,59</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,24</t>
+          <t>0,14; 1,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,71</t>
+          <t>0,28; 1,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,02</t>
+          <t>0,0; 1,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,07</t>
+          <t>0,12; 1,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,6</t>
+          <t>0,0; 0,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,71</t>
+          <t>0,08; 0,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,94</t>
+          <t>0,15; 0,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,88</t>
+          <t>0,14; 0,84</t>
         </is>
       </c>
     </row>
@@ -902,42 +903,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 3,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,0</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,61</t>
+          <t>0,16; 1,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,68</t>
+          <t>0,18; 1,76</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,14</t>
+          <t>0,17; 1,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,22</t>
+          <t>0,19; 1,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,67</t>
+          <t>0,4; 1,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,14</t>
+          <t>0,28; 1,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,97</t>
+          <t>0,17; 0,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,77</t>
+          <t>0,08; 0,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,91</t>
+          <t>0,28; 0,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,84</t>
+          <t>0,24; 0,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,94</t>
+          <t>0,32; 0,96</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen trastornos huesos, articulaciones o musculares (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1296</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2648</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4571</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5063</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4967</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4595</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>660; 6041</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4553</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5869</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1398</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3400</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2788</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4024</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3988</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5699</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>629; 5919</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1300; 7680</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5530</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>607; 5332</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3348</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>706; 6910</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1407; 9048</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1374; 8118</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1442</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1255</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1361</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1885</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1442</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2616</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2660</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5651</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4731</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4763</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4831</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>526; 5270</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4935</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>639; 6351</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3220</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3498</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6235</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7321</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>6765</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>8183</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1184; 7671</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1355; 7909</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2847; 11565</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2023; 8878</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1266; 6645</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>584; 5077</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3968; 12917</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>3536; 12857</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>4688; 13915</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1008-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1008-Estudios-trans_dic.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,03</t>
+          <t>0,0; 4,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -688,17 +688,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,53</t>
+          <t>0,0; 8,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,72</t>
+          <t>0,0; 5,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,5</t>
+          <t>0,0; 5,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,4</t>
+          <t>0,38; 3,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,59</t>
+          <t>0,0; 3,87</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,32</t>
+          <t>0,14; 1,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,63</t>
+          <t>0,29; 1,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,08</t>
+          <t>0,12; 1,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,77</t>
+          <t>0,08; 0,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,96</t>
+          <t>0,2; 0,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,84</t>
+          <t>0,15; 0,89</t>
         </is>
       </c>
     </row>
@@ -898,22 +898,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,42</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,01</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,59</t>
+          <t>0,16; 1,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,76</t>
+          <t>0,18; 1,69</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,13</t>
+          <t>0,17; 1,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,12</t>
+          <t>0,19; 1,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,64</t>
+          <t>0,4; 1,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,23</t>
+          <t>0,19; 1,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,89</t>
+          <t>0,17; 1,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,68</t>
+          <t>0,08; 0,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,92</t>
+          <t>0,28; 0,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,88</t>
+          <t>0,23; 0,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,96</t>
+          <t>0,29; 0,95</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4571</t>
+          <t>0; 3923</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5063</t>
+          <t>0; 5056</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4967</t>
+          <t>0; 4712</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4595</t>
+          <t>0; 4285</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1336,17 +1336,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>660; 6041</t>
+          <t>673; 6477</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4553</t>
+          <t>0; 4573</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5869</t>
+          <t>0; 4949</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5699</t>
+          <t>0; 4908</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>629; 5919</t>
+          <t>628; 6132</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1300; 7680</t>
+          <t>1350; 8175</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5530</t>
+          <t>0; 4480</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>607; 5332</t>
+          <t>608; 5953</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3348</t>
+          <t>0; 2679</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>706; 6910</t>
+          <t>707; 6941</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1407; 9048</t>
+          <t>1921; 8167</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1374; 8118</t>
+          <t>1398; 8590</t>
         </is>
       </c>
     </row>
@@ -1632,22 +1632,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2660</t>
+          <t>0; 2218</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5651</t>
+          <t>0; 4921</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4731</t>
+          <t>0; 4426</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4763</t>
+          <t>0; 4115</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,22 +1657,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4831</t>
+          <t>0; 4836</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>526; 5270</t>
+          <t>525; 5048</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4935</t>
+          <t>0; 4545</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>639; 6351</t>
+          <t>641; 6073</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1184; 7671</t>
+          <t>1183; 7365</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1355; 7909</t>
+          <t>1358; 8233</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2847; 11565</t>
+          <t>2826; 11751</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2023; 8878</t>
+          <t>1386; 9387</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1266; 6645</t>
+          <t>1249; 7664</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>584; 5077</t>
+          <t>587; 5421</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3968; 12917</t>
+          <t>3970; 12494</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3536; 12857</t>
+          <t>3362; 12011</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4688; 13915</t>
+          <t>4209; 13786</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1008-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1008-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,43%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,66%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,37 +678,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,32</t>
+          <t>0,0; 5,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 5,68</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,51</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,43</t>
+          <t>0,0; 4,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 9,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,64</t>
+          <t>0,38; 3,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,87</t>
+          <t>0,0; 4,96</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,72%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,36</t>
+          <t>0,12; 1,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,73</t>
+          <t>0,0; 0,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,21</t>
+          <t>0,14; 1,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,55</t>
+          <t>0,28; 1,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,78</t>
+          <t>0,08; 0,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,87</t>
+          <t>0,2; 0,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,89</t>
+          <t>0,15; 0,88</t>
         </is>
       </c>
     </row>
@@ -845,27 +845,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,87%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,58</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,52</t>
+          <t>0,16; 1,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,69</t>
+          <t>0,18; 1,68</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,89%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,08</t>
+          <t>0,25; 1,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,16</t>
+          <t>0,16; 0,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,67</t>
+          <t>0,08; 0,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,3</t>
+          <t>0,17; 1,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,03</t>
+          <t>0,19; 1,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,73</t>
+          <t>0,41; 1,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,89</t>
+          <t>0,29; 0,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,83</t>
+          <t>0,23; 0,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,95</t>
+          <t>0,29; 0,94</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1205,27 +1205,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>1296</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1579</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1353</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1299</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3923</t>
+          <t>0; 4659</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0; 4749</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0; 5056</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4712</t>
+          <t>0; 4089</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4285</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5370</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>673; 6477</t>
+          <t>670; 6549</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4573</t>
+          <t>0; 4580</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4949</t>
+          <t>0; 6342</t>
         </is>
       </c>
     </row>
@@ -1373,22 +1373,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1398</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2055</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3400</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1390</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4908</t>
+          <t>0; 4852</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>628; 6132</t>
+          <t>607; 5288</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1350; 8175</t>
+          <t>0; 2945</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4480</t>
+          <t>0; 5288</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>608; 5953</t>
+          <t>626; 5590</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2679</t>
+          <t>1299; 8070</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>707; 6941</t>
+          <t>685; 6356</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1921; 8167</t>
+          <t>1921; 8892</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1398; 8590</t>
+          <t>1407; 8418</t>
         </is>
       </c>
     </row>
@@ -1526,27 +1526,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1361</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1442</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1255</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1358</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1361</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2218</t>
+          <t>0; 4749</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4921</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4426</t>
+          <t>0; 4867</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4115</t>
+          <t>0; 2664</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4766</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4836</t>
+          <t>0; 4012</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>525; 5048</t>
+          <t>527; 5349</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4545</t>
+          <t>0; 5503</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>641; 6073</t>
+          <t>639; 6065</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>3220</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>3498</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>6235</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4101</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3267</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1949</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1183; 7365</t>
+          <t>1785; 8224</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1358; 8233</t>
+          <t>1219; 7214</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2826; 11751</t>
+          <t>588; 5708</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1386; 9387</t>
+          <t>1167; 7780</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1249; 7664</t>
+          <t>1360; 8640</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>587; 5421</t>
+          <t>2906; 11767</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3970; 12494</t>
+          <t>3999; 12735</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3362; 12011</t>
+          <t>3398; 12265</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4209; 13786</t>
+          <t>4177; 13601</t>
         </is>
       </c>
     </row>
